--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,49 +795,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135829601</v>
+        <v>137372670</v>
       </c>
       <c r="B3" t="n">
-        <v>57807</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102118</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Åvaviken, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692406</v>
+        <v>692350</v>
       </c>
       <c r="R3" t="n">
-        <v>6562560</v>
+        <v>6562312</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,22 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:53</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>21:53</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,33 +877,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135829601</t>
+          <t>https://artportalen.se/Sighting/137372670</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134319154</v>
+        <v>137372822</v>
       </c>
       <c r="B4" t="n">
-        <v>56539</v>
+        <v>93499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,31 +912,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692407</v>
+        <v>692371</v>
       </c>
       <c r="R4" t="n">
-        <v>6562339</v>
+        <v>6562535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,6 +1000,232 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137372822</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135829601</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57807</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>S Åvaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>692406</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6562560</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalarö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135829601</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134319154</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56539</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S Åvaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>692407</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6562339</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalarö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134319154</t>
         </is>
@@ -1024,6 +1236,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137372670</v>
       </c>
       <c r="B3" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>137372822</v>
       </c>
       <c r="B4" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137372670</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>137372822</v>
       </c>
       <c r="B4" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,32 +795,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137372670</v>
+        <v>137437118</v>
       </c>
       <c r="B3" t="n">
-        <v>92190</v>
+        <v>92592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,14 +829,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S Åvaviken, Srm</t>
+          <t>NO Gråhem, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692350</v>
+        <v>692427</v>
       </c>
       <c r="R3" t="n">
-        <v>6562312</v>
+        <v>6562593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,12 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,16 +895,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137372670</t>
+          <t>https://artportalen.se/Sighting/137437118</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137372822</v>
+        <v>137372670</v>
       </c>
       <c r="B4" t="n">
-        <v>93507</v>
+        <v>92202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692371</v>
+        <v>692350</v>
       </c>
       <c r="R4" t="n">
-        <v>6562535</v>
+        <v>6562312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,55 +1001,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137372822</t>
+          <t>https://artportalen.se/Sighting/137372670</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135829601</v>
+        <v>137372822</v>
       </c>
       <c r="B5" t="n">
-        <v>57807</v>
+        <v>93519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102118</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Åvaviken, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692406</v>
+        <v>692371</v>
       </c>
       <c r="R5" t="n">
-        <v>6562560</v>
+        <v>6562535</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,22 +1075,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>21:53</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>21:53</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,50 +1089,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135829601</t>
+          <t>https://artportalen.se/Sighting/137372822</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134319154</v>
+        <v>135829601</v>
       </c>
       <c r="B6" t="n">
-        <v>56539</v>
+        <v>57807</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>102118</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1153,23 +1143,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Åvaviken, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692407</v>
+        <v>692406</v>
       </c>
       <c r="R6" t="n">
-        <v>6562339</v>
+        <v>6562560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,12 +1182,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,16 +1212,232 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135829601</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137437479</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>N Vinåker, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>692399</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6562275</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalarö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137437479</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134319154</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56539</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>S Åvaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>692407</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6562339</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalarö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134319154</t>
         </is>
@@ -1238,6 +1450,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137437118</v>
       </c>
       <c r="B3" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>137372670</v>
       </c>
       <c r="B4" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>137372822</v>
       </c>
       <c r="B5" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137437118</v>
       </c>
       <c r="B3" t="n">
-        <v>92593</v>
+        <v>92596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>137372670</v>
       </c>
       <c r="B4" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>137372822</v>
       </c>
       <c r="B5" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137437118</v>
       </c>
       <c r="B3" t="n">
-        <v>92596</v>
+        <v>92600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>137372670</v>
       </c>
       <c r="B4" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>137372822</v>
       </c>
       <c r="B5" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137437479</v>
       </c>
       <c r="B7" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
